--- a/artfynd/A 18114-2026 artfynd.xlsx
+++ b/artfynd/A 18114-2026 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133804731</v>
+        <v>133804807</v>
       </c>
       <c r="B3" t="n">
-        <v>91960</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491595</v>
+        <v>491656</v>
       </c>
       <c r="R3" t="n">
-        <v>7035968</v>
+        <v>7035875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133804807</v>
+        <v>133804731</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>91960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491656</v>
+        <v>491595</v>
       </c>
       <c r="R4" t="n">
-        <v>7035875</v>
+        <v>7035968</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133804776</v>
+        <v>133804809</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>92675</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491486</v>
+        <v>491568</v>
       </c>
       <c r="R6" t="n">
-        <v>7035982</v>
+        <v>7036034</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133804787</v>
+        <v>133804741</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491479</v>
+        <v>491478</v>
       </c>
       <c r="R7" t="n">
-        <v>7035758</v>
+        <v>7035918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133804809</v>
+        <v>133804732</v>
       </c>
       <c r="B8" t="n">
-        <v>92675</v>
+        <v>91960</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491568</v>
+        <v>491625</v>
       </c>
       <c r="R8" t="n">
-        <v>7036034</v>
+        <v>7036020</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133804775</v>
+        <v>133804806</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491487</v>
+        <v>491582</v>
       </c>
       <c r="R9" t="n">
-        <v>7036004</v>
+        <v>7035850</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1425,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133804741</v>
+        <v>133804726</v>
       </c>
       <c r="B10" t="n">
         <v>91960</v>
@@ -1501,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491478</v>
+        <v>491629</v>
       </c>
       <c r="R10" t="n">
-        <v>7035918</v>
+        <v>7035933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133804746</v>
+        <v>133804724</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>83344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1574,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491629</v>
+        <v>491525</v>
       </c>
       <c r="R11" t="n">
-        <v>7035971</v>
+        <v>7035801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133804791</v>
+        <v>133804802</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491462</v>
+        <v>491501</v>
       </c>
       <c r="R12" t="n">
-        <v>7035705</v>
+        <v>7035888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1740,7 +1720,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133804765</v>
+        <v>133804737</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1802,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491525</v>
+        <v>491457</v>
       </c>
       <c r="R13" t="n">
-        <v>7036019</v>
+        <v>7035917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1838,11 +1818,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133804732</v>
+        <v>133804796</v>
       </c>
       <c r="B14" t="n">
-        <v>91960</v>
+        <v>58136</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1880,34 +1855,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491625</v>
+        <v>491527</v>
       </c>
       <c r="R14" t="n">
-        <v>7036020</v>
+        <v>7035766</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1966,10 +1953,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133804783</v>
+        <v>133804729</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,21 +1964,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2001,10 +1988,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491477</v>
+        <v>491544</v>
       </c>
       <c r="R15" t="n">
-        <v>7035964</v>
+        <v>7035941</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,11 +2024,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2068,10 +2050,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133804806</v>
+        <v>133804734</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>91960</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,21 +2061,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2103,10 +2085,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491582</v>
+        <v>491594</v>
       </c>
       <c r="R16" t="n">
-        <v>7035850</v>
+        <v>7036064</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,10 +2147,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133804754</v>
+        <v>133804744</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,21 +2158,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2200,10 +2182,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491553</v>
+        <v>491521</v>
       </c>
       <c r="R17" t="n">
-        <v>7036088</v>
+        <v>7035741</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2236,11 +2218,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2267,32 +2244,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133804770</v>
+        <v>133804804</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2302,10 +2279,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491499</v>
+        <v>491517</v>
       </c>
       <c r="R18" t="n">
-        <v>7036018</v>
+        <v>7035921</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2342,7 +2319,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2369,7 +2346,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133804726</v>
+        <v>133804739</v>
       </c>
       <c r="B19" t="n">
         <v>91960</v>
@@ -2404,10 +2381,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491629</v>
+        <v>491457</v>
       </c>
       <c r="R19" t="n">
-        <v>7035933</v>
+        <v>7035921</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2466,7 +2443,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133804778</v>
+        <v>133804749</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2495,16 +2472,24 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491484</v>
+        <v>491517</v>
       </c>
       <c r="R20" t="n">
-        <v>7035977</v>
+        <v>7035916</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,7 +2526,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Gammalt bohål i tajgagrantickerötad död stående gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2568,10 +2553,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133804724</v>
+        <v>133804742</v>
       </c>
       <c r="B21" t="n">
-        <v>83344</v>
+        <v>91960</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2579,21 +2564,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2603,10 +2588,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491525</v>
+        <v>491624</v>
       </c>
       <c r="R21" t="n">
-        <v>7035801</v>
+        <v>7035882</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2665,32 +2650,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133804802</v>
+        <v>133804727</v>
       </c>
       <c r="B22" t="n">
-        <v>99181</v>
+        <v>91960</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2700,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491501</v>
+        <v>491516</v>
       </c>
       <c r="R22" t="n">
-        <v>7035888</v>
+        <v>7035945</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2736,11 +2721,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2767,10 +2747,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133804747</v>
+        <v>133804808</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>83208</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2778,21 +2758,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2802,10 +2782,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491531</v>
+        <v>491558</v>
       </c>
       <c r="R23" t="n">
-        <v>7035902</v>
+        <v>7035850</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2838,11 +2818,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2869,7 +2844,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133804761</v>
+        <v>133804787</v>
       </c>
       <c r="B24" t="n">
         <v>57975</v>
@@ -2904,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491516</v>
+        <v>491479</v>
       </c>
       <c r="R24" t="n">
-        <v>7036045</v>
+        <v>7035758</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2944,7 +2919,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2971,10 +2946,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133804737</v>
+        <v>133804775</v>
       </c>
       <c r="B25" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2982,21 +2957,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3006,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491457</v>
+        <v>491487</v>
       </c>
       <c r="R25" t="n">
-        <v>7035917</v>
+        <v>7036004</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3042,6 +3017,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3068,7 +3048,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133804756</v>
+        <v>133804776</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3103,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491547</v>
+        <v>491486</v>
       </c>
       <c r="R26" t="n">
-        <v>7036083</v>
+        <v>7035982</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3143,7 +3123,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,7 +3150,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133804781</v>
+        <v>133804746</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3205,10 +3185,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491479</v>
+        <v>491629</v>
       </c>
       <c r="R27" t="n">
-        <v>7035968</v>
+        <v>7035971</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3245,7 +3225,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3272,7 +3252,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133804794</v>
+        <v>133804765</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3307,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491583</v>
+        <v>491525</v>
       </c>
       <c r="R28" t="n">
-        <v>7035783</v>
+        <v>7036019</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3347,7 +3327,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3374,10 +3354,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133804734</v>
+        <v>133804791</v>
       </c>
       <c r="B29" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3385,21 +3365,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3409,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491594</v>
+        <v>491462</v>
       </c>
       <c r="R29" t="n">
-        <v>7036064</v>
+        <v>7035705</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3445,6 +3425,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3471,7 +3456,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133804764</v>
+        <v>133804783</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -3506,10 +3491,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491528</v>
+        <v>491477</v>
       </c>
       <c r="R30" t="n">
-        <v>7036028</v>
+        <v>7035964</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3546,7 +3531,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3573,7 +3558,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133804780</v>
+        <v>133804770</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3608,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491483</v>
+        <v>491499</v>
       </c>
       <c r="R31" t="n">
-        <v>7035974</v>
+        <v>7036018</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3675,10 +3660,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133804796</v>
+        <v>133804754</v>
       </c>
       <c r="B32" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,46 +3671,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491527</v>
+        <v>491553</v>
       </c>
       <c r="R32" t="n">
-        <v>7035766</v>
+        <v>7036088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3758,6 +3731,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3784,7 +3762,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133804795</v>
+        <v>133804778</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -3819,10 +3797,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491623</v>
+        <v>491484</v>
       </c>
       <c r="R33" t="n">
-        <v>7035807</v>
+        <v>7035977</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3859,7 +3837,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3886,7 +3864,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133804789</v>
+        <v>133804747</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -3921,10 +3899,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491483</v>
+        <v>491531</v>
       </c>
       <c r="R34" t="n">
-        <v>7035731</v>
+        <v>7035902</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3961,7 +3939,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3988,10 +3966,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133804729</v>
+        <v>133804756</v>
       </c>
       <c r="B35" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3999,21 +3977,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4023,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491544</v>
+        <v>491547</v>
       </c>
       <c r="R35" t="n">
-        <v>7035941</v>
+        <v>7036083</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4059,6 +4037,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4085,7 +4068,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133804752</v>
+        <v>133804761</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4120,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491563</v>
+        <v>491516</v>
       </c>
       <c r="R36" t="n">
-        <v>7036093</v>
+        <v>7036045</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4160,7 +4143,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4187,7 +4170,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133804757</v>
+        <v>133804781</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4222,10 +4205,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491543</v>
+        <v>491479</v>
       </c>
       <c r="R37" t="n">
-        <v>7036068</v>
+        <v>7035968</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4262,7 +4245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4289,7 +4272,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133804762</v>
+        <v>133804764</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4324,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491555</v>
+        <v>491528</v>
       </c>
       <c r="R38" t="n">
-        <v>7036061</v>
+        <v>7036028</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4391,32 +4374,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133804804</v>
+        <v>133804780</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4426,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491517</v>
+        <v>491483</v>
       </c>
       <c r="R39" t="n">
-        <v>7035921</v>
+        <v>7035974</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4466,7 +4449,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>8st bladrosetter</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4493,7 +4476,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133804790</v>
+        <v>133804794</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4528,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491479</v>
+        <v>491583</v>
       </c>
       <c r="R40" t="n">
-        <v>7035726</v>
+        <v>7035783</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4568,7 +4551,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4595,7 +4578,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133804751</v>
+        <v>133804789</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -4630,10 +4613,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>491577</v>
+        <v>491483</v>
       </c>
       <c r="R41" t="n">
-        <v>7036116</v>
+        <v>7035731</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,10 +4680,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133804744</v>
+        <v>133804795</v>
       </c>
       <c r="B42" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4708,21 +4691,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4732,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491521</v>
+        <v>491623</v>
       </c>
       <c r="R42" t="n">
-        <v>7035741</v>
+        <v>7035807</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4768,6 +4751,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4794,7 +4782,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133804792</v>
+        <v>133804752</v>
       </c>
       <c r="B43" t="n">
         <v>57975</v>
@@ -4829,10 +4817,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491463</v>
+        <v>491563</v>
       </c>
       <c r="R43" t="n">
-        <v>7035680</v>
+        <v>7036093</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,10 +4884,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133804739</v>
+        <v>133804757</v>
       </c>
       <c r="B44" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4907,21 +4895,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4931,10 +4919,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491457</v>
+        <v>491543</v>
       </c>
       <c r="R44" t="n">
-        <v>7035921</v>
+        <v>7036068</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4967,6 +4955,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4993,7 +4986,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133804773</v>
+        <v>133804762</v>
       </c>
       <c r="B45" t="n">
         <v>57975</v>
@@ -5028,10 +5021,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491486</v>
+        <v>491555</v>
       </c>
       <c r="R45" t="n">
-        <v>7036001</v>
+        <v>7036061</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5095,7 +5088,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133804749</v>
+        <v>133804790</v>
       </c>
       <c r="B46" t="n">
         <v>57975</v>
@@ -5124,24 +5117,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491517</v>
+        <v>491479</v>
       </c>
       <c r="R46" t="n">
-        <v>7035916</v>
+        <v>7035726</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5178,7 +5163,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gammalt bohål i tajgagrantickerötad död stående gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5205,10 +5190,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133804742</v>
+        <v>133804751</v>
       </c>
       <c r="B47" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5216,21 +5201,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5240,10 +5225,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491624</v>
+        <v>491577</v>
       </c>
       <c r="R47" t="n">
-        <v>7035882</v>
+        <v>7036116</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5276,6 +5261,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5302,7 +5292,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133804771</v>
+        <v>133804792</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5337,10 +5327,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491492</v>
+        <v>491463</v>
       </c>
       <c r="R48" t="n">
-        <v>7036013</v>
+        <v>7035680</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5377,7 +5367,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5404,7 +5394,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133804759</v>
+        <v>133804773</v>
       </c>
       <c r="B49" t="n">
         <v>57975</v>
@@ -5439,10 +5429,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491544</v>
+        <v>491486</v>
       </c>
       <c r="R49" t="n">
-        <v>7036068</v>
+        <v>7036001</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5506,10 +5496,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133804727</v>
+        <v>133804771</v>
       </c>
       <c r="B50" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5517,21 +5507,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5541,10 +5531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491516</v>
+        <v>491492</v>
       </c>
       <c r="R50" t="n">
-        <v>7035945</v>
+        <v>7036013</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5577,6 +5567,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5603,10 +5598,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133804808</v>
+        <v>133804759</v>
       </c>
       <c r="B51" t="n">
-        <v>83208</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5614,21 +5609,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5638,10 +5633,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491558</v>
+        <v>491544</v>
       </c>
       <c r="R51" t="n">
-        <v>7035850</v>
+        <v>7036068</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5674,6 +5669,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 18114-2026 artfynd.xlsx
+++ b/artfynd/A 18114-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133804801</v>
       </c>
       <c r="B2" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133804807</v>
+        <v>133804731</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491656</v>
+        <v>491595</v>
       </c>
       <c r="R3" t="n">
-        <v>7035875</v>
+        <v>7035968</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133804731</v>
+        <v>133804807</v>
       </c>
       <c r="B4" t="n">
-        <v>91960</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491595</v>
+        <v>491656</v>
       </c>
       <c r="R4" t="n">
-        <v>7035968</v>
+        <v>7035875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>133804736</v>
       </c>
       <c r="B5" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>133804809</v>
       </c>
       <c r="B6" t="n">
-        <v>92675</v>
+        <v>92682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>133804741</v>
       </c>
       <c r="B7" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>133804732</v>
       </c>
       <c r="B8" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>133804806</v>
       </c>
       <c r="B9" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>133804726</v>
       </c>
       <c r="B10" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>133804724</v>
       </c>
       <c r="B11" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>133804802</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>133804737</v>
       </c>
       <c r="B13" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133804796</v>
+        <v>133804734</v>
       </c>
       <c r="B14" t="n">
-        <v>58136</v>
+        <v>91967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,46 +1855,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491527</v>
+        <v>491594</v>
       </c>
       <c r="R14" t="n">
-        <v>7035766</v>
+        <v>7036064</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1953,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133804729</v>
+        <v>133804796</v>
       </c>
       <c r="B15" t="n">
-        <v>91960</v>
+        <v>58136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1964,34 +1952,46 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491544</v>
+        <v>491527</v>
       </c>
       <c r="R15" t="n">
-        <v>7035941</v>
+        <v>7035766</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133804734</v>
+        <v>133804729</v>
       </c>
       <c r="B16" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491594</v>
+        <v>491544</v>
       </c>
       <c r="R16" t="n">
-        <v>7036064</v>
+        <v>7035941</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2147,32 +2147,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133804744</v>
+        <v>133804804</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>99188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491521</v>
+        <v>491517</v>
       </c>
       <c r="R17" t="n">
-        <v>7035741</v>
+        <v>7035921</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2218,6 +2218,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2244,32 +2249,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133804804</v>
+        <v>133804744</v>
       </c>
       <c r="B18" t="n">
-        <v>99181</v>
+        <v>91967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2279,10 +2284,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491517</v>
+        <v>491521</v>
       </c>
       <c r="R18" t="n">
-        <v>7035921</v>
+        <v>7035741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2315,11 +2320,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,7 +2349,7 @@
         <v>133804739</v>
       </c>
       <c r="B19" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>133804742</v>
       </c>
       <c r="B21" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>133804727</v>
       </c>
       <c r="B22" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>133804808</v>
       </c>
       <c r="B23" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133804775</v>
+        <v>133804776</v>
       </c>
       <c r="B25" t="n">
         <v>57975</v>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491487</v>
+        <v>491486</v>
       </c>
       <c r="R25" t="n">
-        <v>7036004</v>
+        <v>7035982</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,7 +3048,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133804776</v>
+        <v>133804775</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491486</v>
+        <v>491487</v>
       </c>
       <c r="R26" t="n">
-        <v>7035982</v>
+        <v>7036004</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3252,7 +3252,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133804765</v>
+        <v>133804791</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491525</v>
+        <v>491462</v>
       </c>
       <c r="R28" t="n">
-        <v>7036019</v>
+        <v>7035705</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133804791</v>
+        <v>133804765</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491462</v>
+        <v>491525</v>
       </c>
       <c r="R29" t="n">
-        <v>7035705</v>
+        <v>7036019</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3558,7 +3558,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133804770</v>
+        <v>133804754</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491499</v>
+        <v>491553</v>
       </c>
       <c r="R31" t="n">
-        <v>7036018</v>
+        <v>7036088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3660,7 +3660,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133804754</v>
+        <v>133804770</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491553</v>
+        <v>491499</v>
       </c>
       <c r="R32" t="n">
-        <v>7036088</v>
+        <v>7036018</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3966,7 +3966,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133804756</v>
+        <v>133804761</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491547</v>
+        <v>491516</v>
       </c>
       <c r="R35" t="n">
-        <v>7036083</v>
+        <v>7036045</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4068,7 +4068,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133804761</v>
+        <v>133804756</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4103,10 +4103,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491516</v>
+        <v>491547</v>
       </c>
       <c r="R36" t="n">
-        <v>7036045</v>
+        <v>7036083</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4272,7 +4272,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133804764</v>
+        <v>133804794</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491528</v>
+        <v>491583</v>
       </c>
       <c r="R38" t="n">
-        <v>7036028</v>
+        <v>7035783</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4374,7 +4374,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133804780</v>
+        <v>133804764</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4409,10 +4409,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491483</v>
+        <v>491528</v>
       </c>
       <c r="R39" t="n">
-        <v>7035974</v>
+        <v>7036028</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133804794</v>
+        <v>133804795</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4511,10 +4511,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491583</v>
+        <v>491623</v>
       </c>
       <c r="R40" t="n">
-        <v>7035783</v>
+        <v>7035807</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133804795</v>
+        <v>133804780</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491623</v>
+        <v>491483</v>
       </c>
       <c r="R42" t="n">
-        <v>7035807</v>
+        <v>7035974</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 18114-2026 artfynd.xlsx
+++ b/artfynd/A 18114-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133804801</v>
+        <v>133804809</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491514</v>
+        <v>491568</v>
       </c>
       <c r="R2" t="n">
-        <v>7035734</v>
+        <v>7036034</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133804731</v>
+        <v>133804726</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>491595</v>
+        <v>491629</v>
       </c>
       <c r="R3" t="n">
-        <v>7035968</v>
+        <v>7035933</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133804807</v>
+        <v>133804727</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>491656</v>
+        <v>491516</v>
       </c>
       <c r="R4" t="n">
-        <v>7035875</v>
+        <v>7035945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133804736</v>
+        <v>133804729</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491552</v>
+        <v>491544</v>
       </c>
       <c r="R5" t="n">
-        <v>7035960</v>
+        <v>7035941</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133804809</v>
+        <v>133804731</v>
       </c>
       <c r="B6" t="n">
-        <v>92682</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491568</v>
+        <v>491595</v>
       </c>
       <c r="R6" t="n">
-        <v>7036034</v>
+        <v>7035968</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133804741</v>
+        <v>133804732</v>
       </c>
       <c r="B7" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491478</v>
+        <v>491625</v>
       </c>
       <c r="R7" t="n">
-        <v>7035918</v>
+        <v>7036020</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133804732</v>
+        <v>133804734</v>
       </c>
       <c r="B8" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491625</v>
+        <v>491594</v>
       </c>
       <c r="R8" t="n">
-        <v>7036020</v>
+        <v>7036064</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133804806</v>
+        <v>133804736</v>
       </c>
       <c r="B9" t="n">
-        <v>79366</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491582</v>
+        <v>491552</v>
       </c>
       <c r="R9" t="n">
-        <v>7035850</v>
+        <v>7035960</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133804726</v>
+        <v>133804737</v>
       </c>
       <c r="B10" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491629</v>
+        <v>491457</v>
       </c>
       <c r="R10" t="n">
-        <v>7035933</v>
+        <v>7035917</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133804724</v>
+        <v>133804739</v>
       </c>
       <c r="B11" t="n">
-        <v>83351</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491525</v>
+        <v>491457</v>
       </c>
       <c r="R11" t="n">
-        <v>7035801</v>
+        <v>7035921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133804802</v>
+        <v>133804741</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>91974</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491501</v>
+        <v>491478</v>
       </c>
       <c r="R12" t="n">
-        <v>7035888</v>
+        <v>7035918</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1716,11 +1716,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133804737</v>
+        <v>133804742</v>
       </c>
       <c r="B13" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491457</v>
+        <v>491624</v>
       </c>
       <c r="R13" t="n">
-        <v>7035917</v>
+        <v>7035882</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133804734</v>
+        <v>133804744</v>
       </c>
       <c r="B14" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491594</v>
+        <v>491521</v>
       </c>
       <c r="R14" t="n">
-        <v>7036064</v>
+        <v>7035741</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133804796</v>
+        <v>133804801</v>
       </c>
       <c r="B15" t="n">
-        <v>58136</v>
+        <v>92406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,46 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491527</v>
+        <v>491514</v>
       </c>
       <c r="R15" t="n">
-        <v>7035766</v>
+        <v>7035734</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2050,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133804729</v>
+        <v>133804808</v>
       </c>
       <c r="B16" t="n">
-        <v>91967</v>
+        <v>83222</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2061,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2085,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>491544</v>
+        <v>491558</v>
       </c>
       <c r="R16" t="n">
-        <v>7035941</v>
+        <v>7035850</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2147,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133804804</v>
+        <v>133804806</v>
       </c>
       <c r="B17" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2158,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2182,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491517</v>
+        <v>491582</v>
       </c>
       <c r="R17" t="n">
-        <v>7035921</v>
+        <v>7035850</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2218,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2249,32 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133804744</v>
+        <v>133804807</v>
       </c>
       <c r="B18" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2284,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491521</v>
+        <v>491656</v>
       </c>
       <c r="R18" t="n">
-        <v>7035741</v>
+        <v>7035875</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2346,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133804739</v>
+        <v>133804724</v>
       </c>
       <c r="B19" t="n">
-        <v>91967</v>
+        <v>83358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2357,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2381,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491457</v>
+        <v>491525</v>
       </c>
       <c r="R19" t="n">
-        <v>7035921</v>
+        <v>7035801</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2443,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133804749</v>
+        <v>133804746</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2472,24 +2450,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491517</v>
+        <v>491629</v>
       </c>
       <c r="R20" t="n">
-        <v>7035916</v>
+        <v>7035971</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2496,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gammalt bohål i tajgagrantickerötad död stående gran</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2553,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133804742</v>
+        <v>133804747</v>
       </c>
       <c r="B21" t="n">
-        <v>91967</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2588,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491624</v>
+        <v>491531</v>
       </c>
       <c r="R21" t="n">
-        <v>7035882</v>
+        <v>7035902</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2624,6 +2594,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2650,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133804727</v>
+        <v>133804749</v>
       </c>
       <c r="B22" t="n">
-        <v>91967</v>
+        <v>57975</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2661,34 +2636,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491516</v>
+        <v>491517</v>
       </c>
       <c r="R22" t="n">
-        <v>7035945</v>
+        <v>7035916</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2721,6 +2704,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i tajgagrantickerötad död stående gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2747,10 +2735,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133804808</v>
+        <v>133804751</v>
       </c>
       <c r="B23" t="n">
-        <v>83215</v>
+        <v>57975</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2758,21 +2746,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2782,10 +2770,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491558</v>
+        <v>491577</v>
       </c>
       <c r="R23" t="n">
-        <v>7035850</v>
+        <v>7036116</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2818,6 +2806,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2844,7 +2837,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133804787</v>
+        <v>133804752</v>
       </c>
       <c r="B24" t="n">
         <v>57975</v>
@@ -2879,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491479</v>
+        <v>491563</v>
       </c>
       <c r="R24" t="n">
-        <v>7035758</v>
+        <v>7036093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2946,7 +2939,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133804776</v>
+        <v>133804754</v>
       </c>
       <c r="B25" t="n">
         <v>57975</v>
@@ -2981,10 +2974,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491486</v>
+        <v>491553</v>
       </c>
       <c r="R25" t="n">
-        <v>7035982</v>
+        <v>7036088</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,7 +3014,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,7 +3041,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133804775</v>
+        <v>133804756</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3083,10 +3076,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491487</v>
+        <v>491547</v>
       </c>
       <c r="R26" t="n">
-        <v>7036004</v>
+        <v>7036083</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,7 +3143,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133804746</v>
+        <v>133804757</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3185,10 +3178,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491629</v>
+        <v>491543</v>
       </c>
       <c r="R27" t="n">
-        <v>7035971</v>
+        <v>7036068</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3225,7 +3218,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3252,7 +3245,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133804791</v>
+        <v>133804759</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3287,10 +3280,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491462</v>
+        <v>491544</v>
       </c>
       <c r="R28" t="n">
-        <v>7035705</v>
+        <v>7036068</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3354,7 +3347,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133804765</v>
+        <v>133804761</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3389,10 +3382,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491525</v>
+        <v>491516</v>
       </c>
       <c r="R29" t="n">
-        <v>7036019</v>
+        <v>7036045</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3429,7 +3422,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3456,7 +3449,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133804783</v>
+        <v>133804762</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -3491,10 +3484,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491477</v>
+        <v>491555</v>
       </c>
       <c r="R30" t="n">
-        <v>7035964</v>
+        <v>7036061</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3531,7 +3524,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3558,7 +3551,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133804754</v>
+        <v>133804764</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3593,10 +3586,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>491553</v>
+        <v>491528</v>
       </c>
       <c r="R31" t="n">
-        <v>7036088</v>
+        <v>7036028</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3633,7 +3626,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3660,7 +3653,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133804770</v>
+        <v>133804765</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3695,10 +3688,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491499</v>
+        <v>491525</v>
       </c>
       <c r="R32" t="n">
-        <v>7036018</v>
+        <v>7036019</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3762,7 +3755,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133804778</v>
+        <v>133804766</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -3797,10 +3790,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491484</v>
+        <v>491514</v>
       </c>
       <c r="R33" t="n">
-        <v>7035977</v>
+        <v>7036038</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3864,7 +3857,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133804747</v>
+        <v>133804768</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -3899,10 +3892,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491531</v>
+        <v>491515</v>
       </c>
       <c r="R34" t="n">
-        <v>7035902</v>
+        <v>7036036</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3939,7 +3932,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3966,7 +3959,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133804761</v>
+        <v>133804770</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -4001,10 +3994,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491516</v>
+        <v>491499</v>
       </c>
       <c r="R35" t="n">
-        <v>7036045</v>
+        <v>7036018</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4041,7 +4034,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4068,7 +4061,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133804756</v>
+        <v>133804771</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4103,10 +4096,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491547</v>
+        <v>491492</v>
       </c>
       <c r="R36" t="n">
-        <v>7036083</v>
+        <v>7036013</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4170,7 +4163,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133804781</v>
+        <v>133804773</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4205,10 +4198,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491479</v>
+        <v>491486</v>
       </c>
       <c r="R37" t="n">
-        <v>7035968</v>
+        <v>7036001</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4272,7 +4265,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133804794</v>
+        <v>133804775</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4307,10 +4300,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491583</v>
+        <v>491487</v>
       </c>
       <c r="R38" t="n">
-        <v>7035783</v>
+        <v>7036004</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4374,7 +4367,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133804764</v>
+        <v>133804776</v>
       </c>
       <c r="B39" t="n">
         <v>57975</v>
@@ -4409,10 +4402,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491528</v>
+        <v>491486</v>
       </c>
       <c r="R39" t="n">
-        <v>7036028</v>
+        <v>7035982</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,7 +4469,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133804795</v>
+        <v>133804778</v>
       </c>
       <c r="B40" t="n">
         <v>57975</v>
@@ -4511,10 +4504,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>491623</v>
+        <v>491484</v>
       </c>
       <c r="R40" t="n">
-        <v>7035807</v>
+        <v>7035977</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4551,7 +4544,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4578,7 +4571,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133804789</v>
+        <v>133804780</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -4616,7 +4609,7 @@
         <v>491483</v>
       </c>
       <c r="R41" t="n">
-        <v>7035731</v>
+        <v>7035974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4680,7 +4673,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133804780</v>
+        <v>133804781</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -4715,10 +4708,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491483</v>
+        <v>491479</v>
       </c>
       <c r="R42" t="n">
-        <v>7035974</v>
+        <v>7035968</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4782,7 +4775,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133804752</v>
+        <v>133804783</v>
       </c>
       <c r="B43" t="n">
         <v>57975</v>
@@ -4817,10 +4810,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>491563</v>
+        <v>491477</v>
       </c>
       <c r="R43" t="n">
-        <v>7036093</v>
+        <v>7035964</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4857,7 +4850,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4884,7 +4877,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133804757</v>
+        <v>133804786</v>
       </c>
       <c r="B44" t="n">
         <v>57975</v>
@@ -4919,10 +4912,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491543</v>
+        <v>491483</v>
       </c>
       <c r="R44" t="n">
-        <v>7036068</v>
+        <v>7035782</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4986,7 +4979,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133804762</v>
+        <v>133804787</v>
       </c>
       <c r="B45" t="n">
         <v>57975</v>
@@ -5021,10 +5014,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>491555</v>
+        <v>491479</v>
       </c>
       <c r="R45" t="n">
-        <v>7036061</v>
+        <v>7035758</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5088,7 +5081,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133804790</v>
+        <v>133804789</v>
       </c>
       <c r="B46" t="n">
         <v>57975</v>
@@ -5123,10 +5116,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>491479</v>
+        <v>491483</v>
       </c>
       <c r="R46" t="n">
-        <v>7035726</v>
+        <v>7035731</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5190,7 +5183,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133804751</v>
+        <v>133804790</v>
       </c>
       <c r="B47" t="n">
         <v>57975</v>
@@ -5225,10 +5218,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>491577</v>
+        <v>491479</v>
       </c>
       <c r="R47" t="n">
-        <v>7036116</v>
+        <v>7035726</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5292,7 +5285,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133804792</v>
+        <v>133804791</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5327,10 +5320,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>491463</v>
+        <v>491462</v>
       </c>
       <c r="R48" t="n">
-        <v>7035680</v>
+        <v>7035705</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5394,7 +5387,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133804773</v>
+        <v>133804792</v>
       </c>
       <c r="B49" t="n">
         <v>57975</v>
@@ -5429,10 +5422,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491486</v>
+        <v>491463</v>
       </c>
       <c r="R49" t="n">
-        <v>7036001</v>
+        <v>7035680</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5496,7 +5489,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133804771</v>
+        <v>133804793</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -5531,10 +5524,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491492</v>
+        <v>491463</v>
       </c>
       <c r="R50" t="n">
-        <v>7036013</v>
+        <v>7035678</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5571,7 +5564,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5598,7 +5591,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133804759</v>
+        <v>133804794</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -5633,10 +5626,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>491544</v>
+        <v>491583</v>
       </c>
       <c r="R51" t="n">
-        <v>7036068</v>
+        <v>7035783</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5673,7 +5666,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5700,7 +5693,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133804768</v>
+        <v>133804795</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -5735,10 +5728,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>491515</v>
+        <v>491623</v>
       </c>
       <c r="R52" t="n">
-        <v>7036036</v>
+        <v>7035807</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5775,7 +5768,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5802,10 +5795,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133804793</v>
+        <v>133804796</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5813,34 +5806,46 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Djupdalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>491463</v>
+        <v>491527</v>
       </c>
       <c r="R53" t="n">
-        <v>7035678</v>
+        <v>7035766</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5873,11 +5878,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5904,32 +5904,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133804766</v>
+        <v>133804802</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>491514</v>
+        <v>491501</v>
       </c>
       <c r="R54" t="n">
-        <v>7036038</v>
+        <v>7035888</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6006,32 +6006,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133804786</v>
+        <v>133804804</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6041,10 +6041,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>491483</v>
+        <v>491517</v>
       </c>
       <c r="R55" t="n">
-        <v>7035782</v>
+        <v>7035921</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>8st bladrosetter</t>
         </is>
       </c>
       <c r="AD55" t="b">
